--- a/output/pdf_financials_xlsx/CVV.xlsx
+++ b/output/pdf_financials_xlsx/CVV.xlsx
@@ -6855,43 +6855,43 @@
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>-0.024</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>-0.064</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>0.291</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>0.202</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>0.172</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>-1.791</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0</v>
+        <v>-1.851</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0</v>
+        <v>-1.506</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0</v>
+        <v>-1.643</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0</v>
+        <v>-3.207</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>0</v>
+        <v>-3.857</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>0</v>
+        <v>-6.866</v>
       </c>
     </row>
     <row r="92">
@@ -11168,7 +11168,11 @@
           <t>Investment revaluation reserve (note 8)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -11442,7 +11446,11 @@
           <t>Prepaid and deposits</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -12422,7 +12430,11 @@
           <t>Investment revaluation reserve (note 7)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -12612,7 +12624,11 @@
           <t>Investment revaluation reserve (note 6)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -12712,7 +12728,11 @@
           <t>Investment revaluation reserve</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CVV.xlsx
+++ b/output/pdf_financials_xlsx/CVV.xlsx
@@ -1219,16 +1219,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.28</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.167</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
@@ -1281,16 +1281,16 @@
         </is>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.037</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.386</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.484</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>-0.514</v>
       </c>
     </row>
     <row r="13">
@@ -2494,16 +2494,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.346</v>
+        <v>-3.066</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.823</v>
+        <v>-3.656</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.437</v>
+        <v>-3.349</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.089</v>
+        <v>-1.999</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -2556,16 +2556,16 @@
         </is>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-6.184</v>
+        <v>-6.147</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-9.27</v>
+        <v>-8.884</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-8.037000000000001</v>
+        <v>-7.553</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-10.519</v>
+        <v>-10.005</v>
       </c>
     </row>
     <row r="28">
@@ -2656,16 +2656,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.158</v>
+        <v>-2.878</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.591</v>
+        <v>-3.424</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.226</v>
+        <v>-3.138</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.911</v>
+        <v>-1.821</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -2718,16 +2718,16 @@
         </is>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-6.079</v>
+        <v>-6.042</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-9.102</v>
+        <v>-8.715999999999999</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-7.841</v>
+        <v>-7.357</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-10.336</v>
+        <v>-9.821999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -46168,7 +46168,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -46272,7 +46272,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -47880,7 +47880,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -55306,7 +55306,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E445" s="5" t="n">

--- a/output/pdf_financials_xlsx/CVV.xlsx
+++ b/output/pdf_financials_xlsx/CVV.xlsx
@@ -8109,22 +8109,22 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.079</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.314</v>
       </c>
       <c r="L112" s="3" t="n">
         <v>0</v>
@@ -8136,13 +8136,13 @@
         <v>0</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>0</v>
+        <v>0.096</v>
       </c>
       <c r="R112" s="3" t="n">
         <v>0</v>
@@ -29932,7 +29932,11 @@
           <t>Proceeds from disposition of property and equipment</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -32538,7 +32542,11 @@
           <t>Proceeds from disposition of property and equipment</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -36298,7 +36306,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -36808,7 +36820,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -40468,7 +40484,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CVV.xlsx
+++ b/output/pdf_financials_xlsx/CVV.xlsx
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.298</v>
+        <v>-0.298</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0.268</v>
@@ -8136,13 +8136,13 @@
         <v>0</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>0.096</v>
+        <v>0</v>
       </c>
       <c r="R112" s="3" t="n">
         <v>0</v>
@@ -29932,11 +29932,7 @@
           <t>Proceeds from disposition of property and equipment</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>SaleOfPPE</t>
-        </is>
-      </c>
+      <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -32542,11 +32538,7 @@
           <t>Proceeds from disposition of property and equipment</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>SaleOfPPE</t>
-        </is>
-      </c>
+      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -56046,7 +56038,11 @@
           <t>Future income tax recovery (note 16)</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E452" s="5" t="n">
         <v>0.298</v>
       </c>
